--- a/demo/1_請求_2026年8月.xlsx
+++ b/demo/1_請求_2026年8月.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8月請求" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="雛形" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="雛形_英文" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0&quot; 円&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;¥&quot;#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,18 +35,27 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="20"/>
     </font>
     <font>
-      <sz val="14"/>
-      <u val="single"/>
-    </font>
-    <font>
+      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="16"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="5">
@@ -56,33 +67,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00FFF3D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
     </border>
     <border>
       <left style="thin"/>
@@ -96,28 +101,24 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,16 +484,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -502,25 +495,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>締め日</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>担当</t>
         </is>
@@ -532,21 +530,26 @@
           <t>丸和物流</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>配送業務一式</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D2" t="n">
         <v>4800</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" t="n">
         <v>57600</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>田中</t>
         </is>
@@ -558,21 +561,26 @@
           <t>近江スチール</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>鋼材加工</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="D3" t="n">
         <v>12000</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" t="n">
         <v>60000</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>佐藤</t>
         </is>
@@ -584,21 +592,26 @@
           <t>ヤマノ食品</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>食品仕入</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>28</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D4" t="n">
         <v>1500</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" t="n">
         <v>42000</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>田中</t>
         </is>
@@ -607,50 +620,91 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>北斗精機</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>114000</v>
-      </c>
-      <c r="E5" t="inlineStr">
+          <t>ヤマノ食品</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>冷蔵配送</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>鈴木</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>田中</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>北斗精機</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>精密部品</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>鈴木</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>みどり建設</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>内装工事</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D7" t="n">
         <v>7200</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E7" t="n">
         <v>64800</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>佐藤</t>
         </is>
@@ -670,26 +724,23 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>請　求　書</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>{{取引先}}</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
@@ -699,7 +750,7 @@
           <t>発行日</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026/09/01</t>
         </is>
@@ -713,65 +764,65 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>ご請求金額</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>{{金額}}</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>{{合計:金額}}</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>内訳</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>配送業務一式</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>{{件数}}</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>{{単価}}</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>{{金額}}</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>{{明細:項目}}</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>{{明細:件数}}</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>{{明細:単価}}</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>{{明細:金額}}</t>
         </is>
       </c>
     </row>
@@ -817,4 +868,139 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>INVOICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>{{締め日}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bill To:</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>{{取引先}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rep.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{{担当}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>{{明細:項目}}</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>{{明細:件数}}</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>{{明細:単価}}</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>{{明細:金額}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>{{合計:金額}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Thank you for your business.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/demo/1_請求_2026年8月.xlsx
+++ b/demo/1_請求_2026年8月.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t xml:space="preserve">取引先</t>
   </si>
@@ -39,6 +39,9 @@
     <t xml:space="preserve">金額</t>
   </si>
   <si>
+    <t xml:space="preserve">税込金額</t>
+  </si>
+  <si>
     <t xml:space="preserve">締め日</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
   </si>
   <si>
     <t xml:space="preserve">内装工事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合計</t>
   </si>
   <si>
     <t xml:space="preserve">請　求　書</t>
@@ -791,64 +797,68 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1104,7 +1114,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1123,149 +1133,189 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>4800</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="2" t="n">
         <v>57600</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="0" t="n">
+        <f aca="false">E2*1.1</f>
+        <v>63360</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <f aca="false">E3*1.1</f>
+        <v>66000</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <f aca="false">E4*1.1</f>
+        <v>46200</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <f aca="false">E5*1.1</f>
+        <v>19800</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">E6*1.1</f>
+        <v>125400</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="D7" s="2" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>64800</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <f aca="false">E7*1.1</f>
+        <v>71280</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="H7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>38000</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>114000</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>7200</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>64800</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>13</v>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <f aca="false">SUM(E2:INDEX(E:E,ROW()-1))</f>
+        <v>356400</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <f aca="false">E8*1.1</f>
+        <v>392040</v>
       </c>
     </row>
   </sheetData>
@@ -1287,99 +1337,99 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="20.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>27</v>
+      <c r="A5" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>29</v>
+      <c r="A7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>30</v>
+      <c r="A9" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="B11" s="9" t="s">
         <v>35</v>
       </c>
+      <c r="C11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>37</v>
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>38</v>
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>40</v>
+      <c r="A16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1404,85 +1454,85 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="21.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>41</v>
+      <c r="A1" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
+      <c r="D2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>52</v>
+      <c r="C11" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>53</v>
+      <c r="A13" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
